--- a/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{02EC8B37-9787-4E23-A254-0931D5111ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D680A695-049B-495E-A9A8-73CC57643C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D680A695-049B-495E-A9A8-73CC57643C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{034C1F2B-755A-4018-B8B0-349EF5E4F1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{034C1F2B-755A-4018-B8B0-349EF5E4F1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8A0BE79-CD1A-4EDF-9B5B-799125351086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8A0BE79-CD1A-4EDF-9B5B-799125351086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{306BE373-E6D3-4EFC-9479-BDE618B92FCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{306BE373-E6D3-4EFC-9479-BDE618B92FCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A007DE7-9239-432A-9143-DC41ACD5F64C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A007DE7-9239-432A-9143-DC41ACD5F64C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0AEBCC9-EE5B-45CF-89E4-A0713AAB355E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0AEBCC9-EE5B-45CF-89E4-A0713AAB355E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8647C56B-D983-4DF4-9C4B-D805C994471D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8647C56B-D983-4DF4-9C4B-D805C994471D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD003FC4-8CA8-4F15-9178-A28BEF86CC90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD003FC4-8CA8-4F15-9178-A28BEF86CC90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F08E2A2-DBE1-4373-81D4-F73448D89A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F08E2A2-DBE1-4373-81D4-F73448D89A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F943A99-E733-4EFF-A18E-C73E23326984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F943A99-E733-4EFF-A18E-C73E23326984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA9C678B-DAB3-4924-99AB-863F8B0B8C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA9C678B-DAB3-4924-99AB-863F8B0B8C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{68AAF65D-B2E2-4CFB-A2AC-C1E1C6EB3F3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{68AAF65D-B2E2-4CFB-A2AC-C1E1C6EB3F3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{018D0B38-BAD3-4441-9E10-9A9AB360607A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,6 +40,32 @@
     <author>Amit Kanudia</author>
   </authors>
   <commentList>
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{2FF9EF2B-EBD7-4C7E-9F26-8FF1228838F5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Amit Kanudia:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+11-09-2025
+AFS will be sufficient
+</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D8" authorId="0" shapeId="0" xr:uid="{79577DE7-359E-49C1-A1D9-EC64BAD436CB}">
       <text>
         <r>
@@ -97,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="92">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -358,6 +384,9 @@
   </si>
   <si>
     <t>base-year nuclear capacity</t>
+  </si>
+  <si>
+    <t>\I: hydro</t>
   </si>
   <si>
     <t>windon</t>
@@ -969,15 +998,12 @@
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>6</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="4">
-        <f>IFERROR(VLOOKUP(B5,$F$3:$J$11,5,FALSE),"")</f>
-        <v>0.36680237426422968</v>
-      </c>
+      <c r="D5" s="4"/>
       <c r="F5" t="s">
         <v>6</v>
       </c>
@@ -1185,7 +1211,7 @@
     </row>
     <row r="9" spans="1:38" x14ac:dyDescent="0.45">
       <c r="F9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G9" s="3">
         <v>0.11415525114155252</v>
@@ -1609,12 +1635,12 @@
   <sheetData>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
         <v>69</v>
@@ -1643,7 +1669,7 @@
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -1950,7 +1976,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B9">
         <v>2000</v>
@@ -2062,7 +2088,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B17">
         <v>2001</v>
@@ -2174,7 +2200,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B25">
         <v>2002</v>
@@ -2286,7 +2312,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B33">
         <v>2003</v>
@@ -2398,7 +2424,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B41">
         <v>2004</v>
@@ -2510,7 +2536,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B49">
         <v>2005</v>
@@ -2622,7 +2648,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B57">
         <v>2006</v>
@@ -2734,7 +2760,7 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B65">
         <v>2007</v>
@@ -2846,7 +2872,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B73">
         <v>2008</v>
@@ -2958,7 +2984,7 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B81">
         <v>2009</v>
@@ -3070,7 +3096,7 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B89">
         <v>2010</v>
@@ -3182,7 +3208,7 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B97">
         <v>2011</v>
@@ -3294,7 +3320,7 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B105">
         <v>2012</v>
@@ -3406,7 +3432,7 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B113">
         <v>2013</v>
@@ -3518,7 +3544,7 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B121">
         <v>2014</v>
@@ -3630,7 +3656,7 @@
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B129">
         <v>2015</v>
@@ -3742,7 +3768,7 @@
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B137">
         <v>2016</v>
@@ -3854,7 +3880,7 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B145">
         <v>2017</v>
@@ -3966,7 +3992,7 @@
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B153">
         <v>2018</v>
@@ -4078,7 +4104,7 @@
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B161">
         <v>2019</v>
@@ -4190,7 +4216,7 @@
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B169">
         <v>2020</v>
@@ -4302,7 +4328,7 @@
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B177">
         <v>2021</v>
@@ -4414,7 +4440,7 @@
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B185">
         <v>2022</v>
@@ -4526,7 +4552,7 @@
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B193">
         <v>2023</v>
@@ -4638,7 +4664,7 @@
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B201">
         <v>2000</v>
@@ -4750,7 +4776,7 @@
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A209" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B209">
         <v>2001</v>
@@ -4862,7 +4888,7 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B217">
         <v>2002</v>
@@ -4974,7 +5000,7 @@
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A225" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B225">
         <v>2003</v>
@@ -5086,7 +5112,7 @@
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A233" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B233">
         <v>2004</v>
@@ -5198,7 +5224,7 @@
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A241" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B241">
         <v>2005</v>
@@ -5310,7 +5336,7 @@
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A249" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B249">
         <v>2006</v>
@@ -5422,7 +5448,7 @@
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A257" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B257">
         <v>2007</v>
@@ -5534,7 +5560,7 @@
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A265" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B265">
         <v>2008</v>
@@ -5646,7 +5672,7 @@
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A273" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B273">
         <v>2009</v>
@@ -5758,7 +5784,7 @@
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A281" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B281">
         <v>2010</v>
@@ -5870,7 +5896,7 @@
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A289" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B289">
         <v>2011</v>
@@ -5982,7 +6008,7 @@
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A297" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B297">
         <v>2012</v>
@@ -6094,7 +6120,7 @@
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A305" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B305">
         <v>2013</v>
@@ -6206,7 +6232,7 @@
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A313" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B313">
         <v>2014</v>
@@ -6318,7 +6344,7 @@
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A321" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B321">
         <v>2015</v>
@@ -6430,7 +6456,7 @@
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A329" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B329">
         <v>2016</v>
@@ -6542,7 +6568,7 @@
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A337" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B337">
         <v>2017</v>
@@ -6654,7 +6680,7 @@
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A345" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B345">
         <v>2018</v>
@@ -6766,7 +6792,7 @@
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A353" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B353">
         <v>2019</v>
@@ -6878,7 +6904,7 @@
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A361" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B361">
         <v>2020</v>
@@ -6990,7 +7016,7 @@
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A369" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B369">
         <v>2021</v>
@@ -7102,7 +7128,7 @@
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A377" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B377">
         <v>2022</v>
@@ -7214,7 +7240,7 @@
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A385" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B385">
         <v>2023</v>
@@ -7326,7 +7352,7 @@
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A393" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B393">
         <v>2000</v>
@@ -7438,7 +7464,7 @@
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A401" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B401">
         <v>2001</v>
@@ -7550,7 +7576,7 @@
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A409" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B409">
         <v>2002</v>
@@ -7662,7 +7688,7 @@
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A417" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B417">
         <v>2003</v>
@@ -7774,7 +7800,7 @@
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A425" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B425">
         <v>2004</v>
@@ -7886,7 +7912,7 @@
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A433" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B433">
         <v>2005</v>
@@ -7998,7 +8024,7 @@
     </row>
     <row r="441" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A441" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B441">
         <v>2006</v>
@@ -8110,7 +8136,7 @@
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A449" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B449">
         <v>2007</v>
@@ -8222,7 +8248,7 @@
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A457" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B457">
         <v>2008</v>
@@ -8334,7 +8360,7 @@
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A465" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B465">
         <v>2009</v>
@@ -8446,7 +8472,7 @@
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A473" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B473">
         <v>2010</v>
@@ -8558,7 +8584,7 @@
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A481" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B481">
         <v>2011</v>
@@ -8670,7 +8696,7 @@
     </row>
     <row r="489" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A489" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B489">
         <v>2012</v>
@@ -8782,7 +8808,7 @@
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A497" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B497">
         <v>2013</v>
@@ -8894,7 +8920,7 @@
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A505" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B505">
         <v>2014</v>
@@ -9006,7 +9032,7 @@
     </row>
     <row r="513" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A513" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B513">
         <v>2015</v>
@@ -9118,7 +9144,7 @@
     </row>
     <row r="521" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A521" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B521">
         <v>2016</v>
@@ -9230,7 +9256,7 @@
     </row>
     <row r="529" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A529" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B529">
         <v>2017</v>
@@ -9342,7 +9368,7 @@
     </row>
     <row r="537" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A537" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B537">
         <v>2018</v>
@@ -9454,7 +9480,7 @@
     </row>
     <row r="545" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A545" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B545">
         <v>2019</v>
@@ -9566,7 +9592,7 @@
     </row>
     <row r="553" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A553" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B553">
         <v>2020</v>
@@ -9678,7 +9704,7 @@
     </row>
     <row r="561" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A561" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B561">
         <v>2021</v>
@@ -9790,7 +9816,7 @@
     </row>
     <row r="569" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A569" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B569">
         <v>2022</v>
@@ -9902,7 +9928,7 @@
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A577" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B577">
         <v>2023</v>

--- a/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{018D0B38-BAD3-4441-9E10-9A9AB360607A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4098E8A3-C520-433A-AD97-237FE8DA9CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4098E8A3-C520-433A-AD97-237FE8DA9CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{65CAD222-7C43-419C-9836-3F9196EB3668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{65CAD222-7C43-419C-9836-3F9196EB3668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{595AF279-41D1-4A6C-932A-677632F1F0D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{595AF279-41D1-4A6C-932A-677632F1F0D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5A778CA-CC5A-4DC4-9657-444D747150CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5A778CA-CC5A-4DC4-9657-444D747150CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8059BC6B-FBD4-4B44-83A4-37F6594AC6D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8059BC6B-FBD4-4B44-83A4-37F6594AC6D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3FD9B5EB-8A62-4255-87E4-FC8B1254F176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3FD9B5EB-8A62-4255-87E4-FC8B1254F176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5CFB7E7B-2631-4C07-BB9A-62E9AB8865FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5CFB7E7B-2631-4C07-BB9A-62E9AB8865FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE5EFEBD-4BCE-46FE-A91E-62D8F0EA27F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHE/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE5EFEBD-4BCE-46FE-A91E-62D8F0EA27F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2E362EC-F522-45C9-92B4-B9EC22B760A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
